--- a/preview/pr-13/CodeSystem-wai-skala-5.xlsx
+++ b/preview/pr-13/CodeSystem-wai-skala-5.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:25:29+00:00</t>
+    <t>2026-09-02T07:34:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
